--- a/artfynd/A 24856-2024 artfynd.xlsx
+++ b/artfynd/A 24856-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122743287</v>
+        <v>122743290</v>
       </c>
       <c r="B2" t="n">
-        <v>79843</v>
+        <v>79847</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>740087</v>
+        <v>740059</v>
       </c>
       <c r="R2" t="n">
-        <v>7193656</v>
+        <v>7193708</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -784,7 +784,7 @@
         <v>122743286</v>
       </c>
       <c r="B3" t="n">
-        <v>79843</v>
+        <v>79847</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122743290</v>
+        <v>122743287</v>
       </c>
       <c r="B4" t="n">
-        <v>79843</v>
+        <v>79847</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>740059</v>
+        <v>740087</v>
       </c>
       <c r="R4" t="n">
-        <v>7193708</v>
+        <v>7193656</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 24856-2024 artfynd.xlsx
+++ b/artfynd/A 24856-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122743290</v>
+        <v>122743286</v>
       </c>
       <c r="B2" t="n">
         <v>79847</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>740059</v>
+        <v>740206</v>
       </c>
       <c r="R2" t="n">
-        <v>7193708</v>
+        <v>7193674</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122743286</v>
+        <v>122743287</v>
       </c>
       <c r="B3" t="n">
         <v>79847</v>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>740206</v>
+        <v>740087</v>
       </c>
       <c r="R3" t="n">
-        <v>7193674</v>
+        <v>7193656</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122743287</v>
+        <v>122743290</v>
       </c>
       <c r="B4" t="n">
         <v>79847</v>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>740087</v>
+        <v>740059</v>
       </c>
       <c r="R4" t="n">
-        <v>7193656</v>
+        <v>7193708</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 24856-2024 artfynd.xlsx
+++ b/artfynd/A 24856-2024 artfynd.xlsx
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122743287</v>
+        <v>122743290</v>
       </c>
       <c r="B3" t="n">
         <v>79847</v>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>740087</v>
+        <v>740059</v>
       </c>
       <c r="R3" t="n">
-        <v>7193656</v>
+        <v>7193708</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122743290</v>
+        <v>122743287</v>
       </c>
       <c r="B4" t="n">
         <v>79847</v>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>740059</v>
+        <v>740087</v>
       </c>
       <c r="R4" t="n">
-        <v>7193708</v>
+        <v>7193656</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 24856-2024 artfynd.xlsx
+++ b/artfynd/A 24856-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122743286</v>
+        <v>122743290</v>
       </c>
       <c r="B2" t="n">
         <v>79847</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>740206</v>
+        <v>740059</v>
       </c>
       <c r="R2" t="n">
-        <v>7193674</v>
+        <v>7193708</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122743290</v>
+        <v>122743286</v>
       </c>
       <c r="B3" t="n">
         <v>79847</v>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>740059</v>
+        <v>740206</v>
       </c>
       <c r="R3" t="n">
-        <v>7193708</v>
+        <v>7193674</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 24856-2024 artfynd.xlsx
+++ b/artfynd/A 24856-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122743290</v>
+        <v>122743286</v>
       </c>
       <c r="B2" t="n">
         <v>79847</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>740059</v>
+        <v>740206</v>
       </c>
       <c r="R2" t="n">
-        <v>7193708</v>
+        <v>7193674</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122743286</v>
+        <v>122743290</v>
       </c>
       <c r="B3" t="n">
         <v>79847</v>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>740206</v>
+        <v>740059</v>
       </c>
       <c r="R3" t="n">
-        <v>7193674</v>
+        <v>7193708</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 24856-2024 artfynd.xlsx
+++ b/artfynd/A 24856-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122743290</v>
+        <v>122743286</v>
       </c>
       <c r="B2" t="n">
-        <v>79847</v>
+        <v>79850</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>740059</v>
+        <v>740206</v>
       </c>
       <c r="R2" t="n">
-        <v>7193708</v>
+        <v>7193674</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122743286</v>
+        <v>122743290</v>
       </c>
       <c r="B3" t="n">
-        <v>79847</v>
+        <v>79850</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>740206</v>
+        <v>740059</v>
       </c>
       <c r="R3" t="n">
-        <v>7193674</v>
+        <v>7193708</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,7 +890,7 @@
         <v>122743287</v>
       </c>
       <c r="B4" t="n">
-        <v>79847</v>
+        <v>79850</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 24856-2024 artfynd.xlsx
+++ b/artfynd/A 24856-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122743286</v>
       </c>
       <c r="B2" t="n">
-        <v>79850</v>
+        <v>79852</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122743290</v>
+        <v>122743287</v>
       </c>
       <c r="B3" t="n">
-        <v>79850</v>
+        <v>79852</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>740059</v>
+        <v>740087</v>
       </c>
       <c r="R3" t="n">
-        <v>7193708</v>
+        <v>7193656</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122743287</v>
+        <v>122743290</v>
       </c>
       <c r="B4" t="n">
-        <v>79850</v>
+        <v>79852</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>740087</v>
+        <v>740059</v>
       </c>
       <c r="R4" t="n">
-        <v>7193656</v>
+        <v>7193708</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
